--- a/output/2026-09-01_01_Italia_Liguria_ATEX_Equipment_Services.xlsx
+++ b/output/2026-09-01_01_Italia_Liguria_ATEX_Equipment_Services.xlsx
@@ -493,11 +493,9 @@
           <t>ATEX Equipment/Services - Aspiratori industriali</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rivenditore/assistenza ufficiale BIEMMEDUE, pagine prodotto dedicate 'TT(EX) &amp; TTX(EX) - Aspirapolveri industriali per zone ATEX'. Match diretto e forte col target ATEX/aspirazione. Telefono/email non reperiti pubblicamente.</t>
+          <t>Rivenditore/assistenza ufficiale BIEMMEDUE, pagine prodotto dedicate 'TT(EX) &amp; TTX(EX) - Aspirapolveri industriali per zone ATEX'. Match diretto e forte col target ATEX/aspirazione. Telefono/email non reperiti pubblicamente. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,7 +537,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aspirazione polveri/trucioli/fumi di saldatura e laser, nebbie oleose, ambienti alimentari/medicali. Nessuna certificazione ATEX esplicita trovata, ma coerente con aspirazione industriale generale.</t>
+          <t>Aspirazione polveri/trucioli/fumi di saldatura e laser, nebbie oleose, ambienti alimentari/medicali. Nessuna certificazione ATEX esplicita trovata, ma coerente con aspirazione industriale generale. [DUPLICATO — vedi anche: 2026-08-31_23_Italia_Liguria_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -574,7 +572,6 @@
           <t>010 8380001</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Commercio all'ingrosso di macchine/attrezzature industriali, aspiratori polveri/liquidi per uso industriale e civile. Nessuna certificazione ATEX esplicita rilevata.</t>
@@ -619,7 +616,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Impresa esecutrice di pulizie/aspirazione industriale (fanghi/liquidi/polveri, svuotamento silos) su impianti a carbone, petrolchimico, cementifici. Modello 'impresa esecutrice' più che distributore di macchine.</t>
+          <t>Impresa esecutrice di pulizie/aspirazione industriale (fanghi/liquidi/polveri, svuotamento silos) su impianti a carbone, petrolchimico, cementifici. Modello 'impresa esecutrice' più che distributore di macchine. [DUPLICATO — vedi anche: 2026-08-31_22_Italia_Liguria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -654,10 +651,9 @@
           <t>019 2216947 / 393 3693920</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vendita e noleggio aspiratori industriali/liquidi IPC per Genova, Savona, Imperia.</t>
+          <t>Vendita e noleggio aspiratori industriali/liquidi IPC per Genova, Savona, Imperia. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -699,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ATTENZIONE: core business prevalente è nebulizzazione/raffrescamento outdoor; abbattimento polveri per soppressione a spruzzo nebbia, non aspirazione/captazione come gli altri candidati.</t>
+          <t>ATTENZIONE: core business prevalente è nebulizzazione/raffrescamento outdoor; abbattimento polveri per soppressione a spruzzo nebbia, non aspirazione/captazione come gli altri candidati. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
